--- a/www/download/COUNTRY.POL.rpO2.xlsx
+++ b/www/download/COUNTRY.POL.rpO2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>Polônia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>2.42412495735975</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>2.69164505131081</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>3.26679958645285</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>3.47270458662722</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>3.95882797122747</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>4.33914775167024</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>4.09198792933865</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>4.07830354787578</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>3.88742031091487</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>3.6387453558442</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>3.23185325766701</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>3.10019827648708</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>2.75793607453417</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.37751058134273</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.09692432732096</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14.735</t>
+          <t>-0.488431693176546</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>15.021</t>
+          <t>-0.548665581517868</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15.439</t>
+          <t>-0.464410189891025</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>-0.592960222677894</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>15.375</t>
+          <t>-0.630001550308052</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>15.018</t>
+          <t>-0.700678076364031</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>14.195</t>
+          <t>-0.627874141337621</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13.766</t>
+          <t>-0.618500504347875</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>13.606</t>
+          <t>-0.587303088261538</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>13.773</t>
+          <t>-0.626962139327383</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>14.075</t>
+          <t>-0.632732667139753</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>-0.641856426920193</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>15.174</t>
+          <t>-0.642938005872559</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>15.784</t>
+          <t>-0.635507769156658</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>15.786</t>
+          <t>-0.541333995956817</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8.714</t>
+          <t>-0.179886551057528</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.725</t>
+          <t>-0.27396514764761</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8.863</t>
+          <t>-0.133678929718592</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>8.938</t>
+          <t>-0.337963356118015</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8.896</t>
+          <t>-0.398414755825581</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9.354</t>
+          <t>-0.512744226936162</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10.207</t>
+          <t>-0.394475416099037</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>-0.361893879886209</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>9.891</t>
+          <t>-0.349354694304641</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>10.084</t>
+          <t>-0.387059129824993</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>10.436</t>
+          <t>-0.406511567749557</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>10.963</t>
+          <t>-0.425517712343009</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>11.605</t>
+          <t>-0.419790613048843</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>12.126</t>
+          <t>-0.426785835211918</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>12.207</t>
+          <t>-0.285382282880975</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>28305.086</t>
+          <t>0.0609880331528274</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>28879.294</t>
+          <t>-0.0594361025057426</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29662.441</t>
+          <t>0.12409005166939</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30129.465</t>
+          <t>-0.140443055570731</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>29829.818</t>
+          <t>-0.218203567010599</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>28892.502</t>
+          <t>-0.365660500922984</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>26456.571</t>
+          <t>-0.202646739187441</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>25507.399</t>
+          <t>-0.156033443354238</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>25162.379</t>
+          <t>-0.4115163875513</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>25538.377</t>
+          <t>-0.188775102130418</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>25769.666</t>
+          <t>-0.230640059859658</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>26509.432</t>
+          <t>-0.254342724923429</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>27585.81</t>
+          <t>-0.234399337499636</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>28604.274</t>
+          <t>-0.284894961824228</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>28297.15</t>
+          <t>-0.111058306266389</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15014.242</t>
+          <t>184364716381.107</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15032.708</t>
+          <t>192186319997.857</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15287.945</t>
+          <t>151019536917.238</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15407.358</t>
+          <t>182148838244.531</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15801.55</t>
+          <t>215967786762.224</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>16365.614</t>
+          <t>302206995817.256</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>17542.312</t>
+          <t>312844982687.946</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16854.515</t>
+          <t>335621625466.339</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>16906.382</t>
+          <t>367191756715.836</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>17319.251</t>
+          <t>410562863735.729</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>17709.691</t>
+          <t>505772829303.617</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>18612.378</t>
+          <t>557055227354.662</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>19705.785</t>
+          <t>552063425918.097</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>20418.937</t>
+          <t>489033799565.316</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>20070.824</t>
+          <t>294512880481.212</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>44058020037.0453</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>48588599179.0015</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>42940406341.3082</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>54441371410.7512</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>61896057470.9251</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>77606292632.4718</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>78722249714.1232</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>81536979261.0878</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>23.21</t>
+          <t>82325367734.0269</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>87920336914.7888</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>104535925017.783</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>109320872412.235</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>106392807444.152</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>102988419724.811</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>31.92</t>
+          <t>69840509003.7588</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>21669427.112541</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>21598000.3828793</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>16631066.7639908</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>19359063.5561001</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>24542238.7271212</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>36392217.4941152</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>71.37</t>
+          <t>36383113.7418559</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>36421406.495761</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>68.27</t>
+          <t>35133054.2003624</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>67.04</t>
+          <t>30465572.8196222</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>66.25</t>
+          <t>32250864.0817971</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>30527720.9033847</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>23631853.9101488</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>16920882.2112838</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>13237721.2312409</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>22664.4786708184</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>21374.9754857526</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>20545.1076745729</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>21014.6190329546</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>20657.3440059529</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>12488.7722428034</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>12421.4467018458</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>13785.5341463664</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>13734.8773490957</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>14590.8290229159</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>16101.4513929743</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>16272.3366155638</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>19539.0911905519</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>21912.4343117647</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>25577.9815489854</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>77292.7176819432</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>83664.9437081016</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>64761.2878936435</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>76828.9195000689</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>84826.2533881104</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>93615.8932032266</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>92179.4370272962</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>103917.277163332</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>116239.434003508</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>17.76</t>
+          <t>140387.232430414</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>167178.587442931</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>195136.266199022</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>246460.710359721</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>244291.641337596</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>169913.728651716</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>-0.24327878254384</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>-0.330074559787869</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>-0.202277527242285</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>-0.390954256479066</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>-0.447776825003974</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>-0.553478485456849</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>-0.450190687044043</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.64</t>
+          <t>-0.43119569226563</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>76.03</t>
+          <t>-0.42908823834393</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>-0.466492880525225</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>74.06</t>
+          <t>-0.486026952258068</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>73.47</t>
+          <t>-0.503468777726796</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>72.83</t>
+          <t>-0.501455577753556</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>-0.502083422396211</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>-0.384576414388948</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>32576.0339670849</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>36808.2738750884</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>39096.1452575262</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>42666.8431366874</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>43137.6454940369</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>44093.3977422624</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>46807.1881066426</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>49867.4481896885</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>55784.322017333</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>63773.1867390281</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>72651.060032066</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>78521.8156547962</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>95388.6672297573</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.42412495735975</t>
+          <t>5056.17820639284</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.69164505131081</t>
+          <t>5569.08537588702</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3.26679958645285</t>
+          <t>4844.7971772394</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3.47270458662722</t>
+          <t>6090.72892360503</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3.95882797122747</t>
+          <t>6957.74027326047</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.33914775167024</t>
+          <t>8296.50021193613</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.09198792933865</t>
+          <t>7712.87693395677</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4.07830354787578</t>
+          <t>8253.1483638937</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3.88742031091487</t>
+          <t>8323.4286138661</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3.6387453558442</t>
+          <t>8718.96873349222</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>3.23185325766701</t>
+          <t>10016.5695713791</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3.10019827648708</t>
+          <t>9971.89360591039</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2.75793607453417</t>
+          <t>9167.92108886352</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.37751058134273</t>
+          <t>8493.329901929</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>3.09692432732096</t>
+          <t>5721.48975593394</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>61391138502.3109</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>61298607958.3441</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>34551476513.745</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>51928919496.5462</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>58720589894.9882</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>117361059120.87</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>134967763977.091</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>149713054315.625</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>172863244156.648</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>207514839383.596</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>275982170598.082</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>286826916909.266</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>271872523522.374</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>269126312410.498</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>205459534094.706</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>63905545128.3905</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>60195847620.5647</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>28961110460.2269</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>41978406897.3008</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>58425843535.6515</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>118682326527.196</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>144760588285.923</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>161650218927.767</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>185172745659.194</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>219171455490.317</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>289927103698.572</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>301687502103.258</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>275947200854.445</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>276912336862.995</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>207160190272.353</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>-2514406626.07959</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>1102760337.77947</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.453</t>
+          <t>5590366053.51811</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>9950512599.24538</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>294746359.336713</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>-1321267406.32631</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-9792824308.83222</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.554</t>
+          <t>-11937164612.142</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>-12309501502.5458</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>-11656616106.7211</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>-13944933100.49</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>-14860585193.9926</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.043</t>
+          <t>-4074677332.07079</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7786024452.4967</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1700656177.64705</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>3826.11732801689</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>3730.87197202006</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3864.80358423701</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>3709.53252586148</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>3842.22542449761</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>3704.5658400413</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>4240.61156797262</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>4694.4263417536</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>4751.94329296084</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>4651.63189379606</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>5148.24679052079</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>4951.35652052103</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>4570.61592244845</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>4228.96975722841</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>3521.13974063377</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>5006.75394739016</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>4599.91297138554</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>4463.94134336561</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>4568.68412027134</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>4886.63303735986</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>3999.3189228006</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>4582.55804656421</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>5115.50334285097</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>5136.15629382706</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>5009.90756761746</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>5563.12695293072</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>5269.52299730193</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>4815.53684499971</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>4637.89378638094</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>4739.9238538318</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-48.84</t>
+          <t>32273.0904982147</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-54.87</t>
+          <t>34981.3289632228</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-46.44</t>
+          <t>36927.2736772823</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-59.3</t>
+          <t>44720.5519158438</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-63</t>
+          <t>40164.013906437</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-70.07</t>
+          <t>46634.020946017</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-62.79</t>
+          <t>51317.5554726516</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-61.85</t>
+          <t>55901.6892476891</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-58.73</t>
+          <t>71127.0532923045</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-62.7</t>
+          <t>93780.533903888</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-63.27</t>
+          <t>112144.879107038</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-64.19</t>
+          <t>137120.586339317</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-64.29</t>
+          <t>174806.150409671</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-63.55</t>
+          <t>213238.291851392</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-54.13</t>
+          <t>165890.059090342</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-17.99</t>
+          <t>29228941128.3915</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-27.4</t>
+          <t>29796768099.6027</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-13.37</t>
+          <t>23195214322.1697</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-33.8</t>
+          <t>31683706028.6568</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-39.84</t>
+          <t>36866209918.6808</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-51.27</t>
+          <t>63273022298.0867</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-39.45</t>
+          <t>70088289703.2001</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-36.19</t>
+          <t>80667588676.5404</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-34.94</t>
+          <t>99872266400.9159</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-38.71</t>
+          <t>123029404024.554</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-40.65</t>
+          <t>151247404539.694</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-42.55</t>
+          <t>176548999998.251</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-41.98</t>
+          <t>174151575246.465</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-42.68</t>
+          <t>155047310880.409</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-28.54</t>
+          <t>87325153575.5528</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>27947.9236956013</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>35401.5459044805</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>40806.6375670446</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-14.04</t>
+          <t>50367.1160082573</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-21.82</t>
+          <t>47847.6881637181</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-36.57</t>
+          <t>55163.6032673991</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-20.26</t>
+          <t>55959.0223500399</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-15.6</t>
+          <t>60262.9530736781</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-41.15</t>
+          <t>73868.5240165445</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>95764.783608164</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>109753.160494378</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-25.43</t>
+          <t>137410.611722296</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-23.44</t>
+          <t>179302.879672821</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-28.49</t>
+          <t>225277.374472069</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>158895.392346397</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>73775.521</t>
+          <t>72711197623.5818</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>69093.453</t>
+          <t>92763965295.4213</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>68917.451</t>
+          <t>71069745837.388</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>72187.037</t>
+          <t>104813586159.657</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>75131.983</t>
+          <t>133454385240.926</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>60059.772</t>
+          <t>240580895631.539</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>65048.495</t>
+          <t>240018051463.953</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>70421.554</t>
+          <t>261854865111.435</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>69883.056</t>
+          <t>291724020196.113</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>69002.96</t>
+          <t>343145818708.09</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>78298.23</t>
+          <t>411284886903.634</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>76565.642</t>
+          <t>465173683469.695</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>73071.919</t>
+          <t>466770220031.377</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>73202.873</t>
+          <t>472717446707.325</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>74825.174</t>
+          <t>270108609188.77</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>33339.639</t>
+          <t>4325.16680261337</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>32550.739</t>
+          <t>-420.216941257668</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>34254.527</t>
+          <t>-3879.3638897623</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>33157.286</t>
+          <t>-5646.5640924135</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>34180.437</t>
+          <t>-7683.67425728115</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>34652.879</t>
+          <t>-8529.58232138208</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>43282.226</t>
+          <t>-4641.4668773883</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>46378.585</t>
+          <t>-4361.26382598899</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>47000.521</t>
+          <t>-2741.47072423993</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>46906.126</t>
+          <t>-1984.24970427598</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>53728.648</t>
+          <t>2391.71861266029</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>54281.226</t>
+          <t>-290.02538297949</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>53041.541</t>
+          <t>-4496.72926315063</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>51279.641</t>
+          <t>-12039.0826206775</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>42981.496</t>
+          <t>6994.66674394492</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>184364.716</t>
+          <t>-43482256495.1902</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>192186.32</t>
+          <t>-62967197195.8186</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>151019.537</t>
+          <t>-47874531515.2183</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>182148.838</t>
+          <t>-73129880131.0002</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>215967.787</t>
+          <t>-96588175322.2457</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>302206.996</t>
+          <t>-177307873333.452</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>312844.983</t>
+          <t>-169929761760.753</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>335621.625</t>
+          <t>-181187276434.894</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>367191.757</t>
+          <t>-191851753795.197</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>410562.864</t>
+          <t>-220116414683.536</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>505772.829</t>
+          <t>-260037482363.939</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>557055.227</t>
+          <t>-288624683471.444</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>552063.426</t>
+          <t>-292618644784.912</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>489033.8</t>
+          <t>-317670135826.915</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>294512.88</t>
+          <t>-182783455613.218</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>66902.07927</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>72393.64547</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>71058.53687</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76788.56472</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>72655.5947</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>73159.29721</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>78760.74134</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>80203.44746</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>89780.8755</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>107873.44568</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>127833.46508</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>143520.73575</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>179221.20543</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>222432.85622</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>184289.98954</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>54061.111</t>
+          <t>-0.0758416078262403</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>49100.348</t>
+          <t>-0.0757022375858964</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>47909.99</t>
+          <t>-0.0850823533383653</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>49822.234</t>
+          <t>-0.0950725202021011</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>52593.633</t>
+          <t>-0.103577164804921</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>40315.744</t>
+          <t>-0.0227658275929951</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>42156.769</t>
+          <t>0.00327696236818935</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>44523.139</t>
+          <t>0.0137438063582751</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>43387.46</t>
+          <t>0.020810741731105</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>42670.921</t>
+          <t>0.039911932707189</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>48712.438</t>
+          <t>0.0466037532633269</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>46452.617</t>
+          <t>0.0590318048770405</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>43766.885</t>
+          <t>0.0661443494075685</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>43865.279</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>44334.528</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>55322.2305835788</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>64243.2401122611</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>65817.015680837</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>72614.0086731007</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>69775.9544477548</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>69008.2517646412</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>78158.5883185697</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>77618.7934548832</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>82843.1121536122</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>91917.3966184302</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>108968.128312447</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>121452.55447037</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>151637.307249389</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>199382.989951675</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>158759.834349227</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>44058.02</t>
+          <t>122419.634625984</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>48588.599</t>
+          <t>136365.178028398</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>42940.406</t>
+          <t>138702.568470208</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>54441.371</t>
+          <t>158088.637722025</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>61896.057</t>
+          <t>154789.819536808</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>77606.293</t>
+          <t>119603.910053449</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>78722.25</t>
+          <t>121330.985757966</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>81536.979</t>
+          <t>117856.895027572</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>82325.368</t>
+          <t>123175.866337015</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>87920.337</t>
+          <t>135218.424879093</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>104535.925</t>
+          <t>158798.181727026</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>109320.872</t>
+          <t>171313.241181191</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>106392.807</t>
+          <t>208900.965393392</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>102988.42</t>
+          <t>271054.618660394</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>69840.509</t>
+          <t>216652.208613619</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-24.33</t>
+          <t>426619.898502123</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-33.01</t>
+          <t>464177.552923918</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-20.23</t>
+          <t>452635.807269903</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-39.1</t>
+          <t>494548.346133708</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-44.78</t>
+          <t>480450.148587969</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-55.35</t>
+          <t>486745.455241911</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-45.02</t>
+          <t>539597.482887317</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-43.12</t>
+          <t>553798.994567247</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-42.91</t>
+          <t>601526.101635378</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-46.65</t>
+          <t>671938.500413658</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-48.6</t>
+          <t>785564.806423376</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-50.35</t>
+          <t>855912.421604851</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-50.15</t>
+          <t>1042806.03475039</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-50.21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-38.46</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>21.669</t>
+          <t>122419.634625984</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>21.598</t>
+          <t>129436.259353255</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>16.631</t>
+          <t>142833.683496869</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>19.359</t>
+          <t>160530.459879988</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>24.542</t>
+          <t>177550.859327161</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>36.392</t>
+          <t>134371.612221007</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>36.383</t>
+          <t>123613.532384102</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>36.421</t>
+          <t>120635.015915468</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>35.133</t>
+          <t>119602.990802215</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>30.466</t>
+          <t>112883.529539395</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>32.251</t>
+          <t>117762.490628025</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>30.528</t>
+          <t>119156.286087209</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>23.632</t>
+          <t>122537.678036396</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>16.921</t>
+          <t>135611.742378845</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>13.238</t>
+          <t>134732.675475313</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>55322.2305835788</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>60999.3820175542</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>66319.2242131613</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>70225.6586635871</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>72995.5337176053</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>73378.843003773</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>75466.455410065</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>72914.3072583563</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>73912.6866171794</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>72988.5945707342</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>75529.0483650772</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>80455.9358743324</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>87439.8862806087</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>97107.2575900012</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>93588.395627913</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>220.494934016407</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1668.99448160193</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>584.825569792097</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-4351.11449202529</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-6626.01872680818</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>33012.2346265512</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>48575.428752034</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>57478.7543324281</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>68302.5263629852</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>90591.5509509075</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>109261.328442974</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>129047.870718809</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>164364.393956608</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>198544.131219606</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>168885.787786381</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>33339638561.1408</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>32550738694.2834</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>34254527127.8094</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>33157285529.1603</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>34180437376.3308</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>34652879324.3303</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>43282226029.6693</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>46378585043.3547</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>47000520722.0171</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>46906125690.6607</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>53728647979.9121</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>54281226398.82</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>53041540718.422</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>51279641482.2003</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>42981496471.9942</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>73775520765.5835</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>69093452777.9936</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>68917451217.8186</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>72187036573.9352</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>75131982949.4079</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>60059771923.158</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>65048494959.3697</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>70421553668.6893</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>69883056149.4404</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>69002959901.0656</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>78298230299.0234</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>76565642198.4974</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>73071919193.3945</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>73202873197.6875</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>74825174404.4269</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>54061110896.1854</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>49100348324.9031</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>47909989869.6321</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>49822234490.759</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52593633305.2388</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>40315743532.4611</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>42156769489.1375</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>44523139023.8714</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>43387459559.8838</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>42670921309.714</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>48712438306.1273</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>46452616674.1828</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>43766885221.739</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>43865279018.6912</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>44334528367.2044</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>14735200</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>15020600</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>15438700</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>15800400</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>15375000</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>15017500</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>14194800</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>13766300</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>13606100</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>13773300</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>14074500</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>14529900</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>15174200</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>15783645.889573</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>15786155.3712382</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>8713700</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>8724700</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>8863200</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>8938400</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>8896000</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>9354100</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10206600</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>9879500</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>9890800</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>10083800</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>10436300</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>10962900</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>11604900</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>12125800</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>12206700</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>28305086293.1525</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>28879294419.0028</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>29662440618.8973</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>30129464561.2833</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>29829817522.3089</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>28892502127.8591</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>26456570789.3266</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>25507398965.6909</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>25162379461.1629</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>25538377300.9695</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>25769666149.1946</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>26509432484.7037</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>27585810137.3996</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>28604273526.7837</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>28297149673.6112</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>15014241815.3346</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>15032707867.3007</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>15287944968.716</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>15407358482.0686</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>15801550161.6009</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>16365614284.9565</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>17542311839.8331</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>16854514610.4582</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>16906382225.1846</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>17319250893.9937</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>17709690793.7366</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>18612378276.4895</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>19705785159.2337</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>20418936958.2142</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>20070824201.2121</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.197493838927671</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.197493838927671</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.197493838927671</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.197493838927671</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.197493838927671</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.197493838927671</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.214380705497248</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.230918530591076</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.232116469535008</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.277251635777324</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.288095700635141</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.295513218664395</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.304555318021329</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.299157843309884</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.319155072994049</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.728913401470213</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.728913401470213</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.728913401470213</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.728913401470213</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.728913401470213</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.728913401470213</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.713749162074466</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.704022519621681</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.682689167535268</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.67044334674335</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.662467146601343</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.656010408643502</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.646989663617845</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.649286049704992</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.631515982679652</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.0735927596021157</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.0735927596021157</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.0735927596021157</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.0735927596021157</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0735927596021157</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0735927596021157</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.0718701324282859</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.0650589497872431</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.0851943629297249</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0523050174793255</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0494371527635151</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0484763726921036</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0484550183608254</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0515561069851239</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0493289443262993</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.122043564712389</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.122043564712389</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.122043564712389</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.122043564712389</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.122043564712389</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.122043564712389</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.133271213275365</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.141719800156731</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.156956740225659</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.17755604537419</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.188549726720077</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.196122066802558</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.201049411020539</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.203680734714193</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.220249348393439</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.776542665775152</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.776542665775152</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.776542665775152</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.776542665775152</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.776542665775152</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.776542665775152</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.766039863441556</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.766362663654355</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.760297201690192</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.746768404993518</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.740576730084175</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.734687391152289</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.728261829122457</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.723964954159925</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.70997595536251</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.101413769512459</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.101413769512459</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.101413769512459</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.101413769512459</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.101413769512459</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.101413769512459</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.100688923283079</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0919175361889144</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0827460580841493</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0756755496322918</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.070873543195748</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0691905420451524</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0706887598570042</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0723543111258817</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0697746962440506</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>264793.69278</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>299043.88961</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>300257.78319</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>329628.38256</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>320451.15519</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>335095.52743</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>374515.27799</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>384060.67339</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>424185.41114</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>509518.75332</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>603836.20512</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>695167.79525</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>883621.63806</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1111403.68187</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>865782.85723</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>122640.12956</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>138034.17251</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>139287.39404</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>153737.52323</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>148163.80081</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>152616.14468</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>169906.41451</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>175335.64936</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>191478.3927</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>225809.97583</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>268059.51017</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>300361.1119</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>373265.35935</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>469598.74988</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>385537.9964</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1034179.94551128</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1062964.04076036</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1105245.96981106</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1156671.62373569</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1210867.2853591</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1263983.15299466</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1302898.57441767</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1332205.72669073</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1359887.13054996</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1391996.40648563</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1428955.21337048</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1479953.99581784</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1549336.65184272</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
